--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Medium Term Bond Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Medium Term Bond Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="199">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential Medium Term Bond Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -70,21 +70,57 @@
     <t>SOV</t>
   </si>
   <si>
+    <t>IN0020240035</t>
+  </si>
+  <si>
     <t>IN0020240126</t>
   </si>
   <si>
-    <t>IN0020220151</t>
+    <t>IN0020240118</t>
+  </si>
+  <si>
+    <t>State Government of Maharashtra</t>
+  </si>
+  <si>
+    <t>IN2220240435</t>
+  </si>
+  <si>
+    <t>IN2220240427</t>
+  </si>
+  <si>
+    <t>State Government of Chhattisgarh</t>
+  </si>
+  <si>
+    <t>IN3520240083</t>
+  </si>
+  <si>
+    <t>State Government of Karnataka</t>
+  </si>
+  <si>
+    <t>IN1920240257</t>
+  </si>
+  <si>
+    <t>State Government of West Bengal</t>
+  </si>
+  <si>
+    <t>IN3420240241</t>
   </si>
   <si>
     <t>IN0020240134</t>
   </si>
   <si>
-    <t>IN0020230085</t>
-  </si>
-  <si>
     <t>Non-Convertible debentures / Bonds</t>
   </si>
   <si>
+    <t>Vedanta Ltd. **</t>
+  </si>
+  <si>
+    <t>INE205A08038</t>
+  </si>
+  <si>
+    <t>ICRA AA</t>
+  </si>
+  <si>
     <t>Godrej Properties Ltd. **</t>
   </si>
   <si>
@@ -103,6 +139,48 @@
     <t>CARE AA+</t>
   </si>
   <si>
+    <t>Tata Projects Ltd. **</t>
+  </si>
+  <si>
+    <t>INE725H08246</t>
+  </si>
+  <si>
+    <t>FITCH AA</t>
+  </si>
+  <si>
+    <t>Macrotech Developers Ltd. **</t>
+  </si>
+  <si>
+    <t>INE670K07273</t>
+  </si>
+  <si>
+    <t>CRISIL AA</t>
+  </si>
+  <si>
+    <t>TVS Credit Services Ltd. **</t>
+  </si>
+  <si>
+    <t>INE729N08089</t>
+  </si>
+  <si>
+    <t>CRISIL AA+</t>
+  </si>
+  <si>
+    <t>Ess Kay Fincorp Ltd **</t>
+  </si>
+  <si>
+    <t>INE124N07721</t>
+  </si>
+  <si>
+    <t>ICRA AA-</t>
+  </si>
+  <si>
+    <t>Torrent Power Ltd. **</t>
+  </si>
+  <si>
+    <t>INE813H07366</t>
+  </si>
+  <si>
     <t>Pipeline Infrastructure Pvt Ltd. **</t>
   </si>
   <si>
@@ -112,64 +190,85 @@
     <t>CRISIL AAA</t>
   </si>
   <si>
-    <t>Macrotech Developers Ltd. **</t>
-  </si>
-  <si>
-    <t>INE670K07273</t>
+    <t>Nirma Ltd. **</t>
+  </si>
+  <si>
+    <t>INE091A07208</t>
+  </si>
+  <si>
+    <t>SEIL Energy India Ltd. **</t>
+  </si>
+  <si>
+    <t>INE460M07010</t>
+  </si>
+  <si>
+    <t>G R Infraprojects Ltd. **</t>
+  </si>
+  <si>
+    <t>INE201P08209</t>
+  </si>
+  <si>
+    <t>Jhajjar Power Ltd. **</t>
+  </si>
+  <si>
+    <t>INE165K07027</t>
+  </si>
+  <si>
+    <t>FITCH AA(CE)</t>
+  </si>
+  <si>
+    <t>INE484J08071</t>
+  </si>
+  <si>
+    <t>Oriental Nagpur Betul Highway Ltd. **</t>
+  </si>
+  <si>
+    <t>INE105N07209</t>
+  </si>
+  <si>
+    <t>Eris Lifesciences Ltd. **</t>
+  </si>
+  <si>
+    <t>INE406M08029</t>
+  </si>
+  <si>
+    <t>INE406M08011</t>
+  </si>
+  <si>
+    <t>360 One Prime Ltd. **</t>
+  </si>
+  <si>
+    <t>INE248U07FN4</t>
+  </si>
+  <si>
+    <t>Avanse Financial Services Ltd **</t>
+  </si>
+  <si>
+    <t>INE087P07444</t>
   </si>
   <si>
     <t>CRISIL AA-</t>
   </si>
   <si>
-    <t>TVS Credit Services Ltd. **</t>
-  </si>
-  <si>
-    <t>INE729N08089</t>
-  </si>
-  <si>
-    <t>CRISIL AA</t>
-  </si>
-  <si>
-    <t>Ess Kay Fincorp Ltd **</t>
-  </si>
-  <si>
-    <t>INE124N07721</t>
-  </si>
-  <si>
-    <t>ICRA AA-</t>
-  </si>
-  <si>
-    <t>Torrent Power Ltd. **</t>
-  </si>
-  <si>
-    <t>INE813H07366</t>
-  </si>
-  <si>
-    <t>CRISIL AA+</t>
-  </si>
-  <si>
-    <t>Nirma Ltd. **</t>
-  </si>
-  <si>
-    <t>INE091A07208</t>
-  </si>
-  <si>
-    <t>IIFL Home Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE477L07AV2</t>
-  </si>
-  <si>
-    <t>G R Infraprojects Ltd. **</t>
-  </si>
-  <si>
-    <t>INE201P08209</t>
-  </si>
-  <si>
-    <t>SEIL Energy India Ltd. **</t>
-  </si>
-  <si>
-    <t>INE460M07010</t>
+    <t>INE729N08113</t>
+  </si>
+  <si>
+    <t>Aadhar Housing Finance Ltd. **</t>
+  </si>
+  <si>
+    <t>INE883F07397</t>
+  </si>
+  <si>
+    <t>CARE AA</t>
+  </si>
+  <si>
+    <t>Cholamandalam Investment And Finance Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE121A08PP7</t>
+  </si>
+  <si>
+    <t>INE729N08097</t>
   </si>
   <si>
     <t>Kalpataru Projects International Ltd **</t>
@@ -178,121 +277,70 @@
     <t>INE220B08142</t>
   </si>
   <si>
-    <t>FITCH AA</t>
-  </si>
-  <si>
-    <t>Jhajjar Power Ltd. **</t>
-  </si>
-  <si>
-    <t>INE165K07027</t>
-  </si>
-  <si>
-    <t>FITCH AA(CE)</t>
-  </si>
-  <si>
-    <t>Oriental Nagpur Betul Highway Ltd. **</t>
-  </si>
-  <si>
-    <t>INE105N07209</t>
-  </si>
-  <si>
-    <t>INE484J08071</t>
-  </si>
-  <si>
-    <t>Eris Lifesciences Ltd. **</t>
-  </si>
-  <si>
-    <t>INE406M08029</t>
-  </si>
-  <si>
-    <t>FITCH AA-</t>
-  </si>
-  <si>
-    <t>INE406M08011</t>
+    <t>Bharat Sanchar Nigam Ltd. **</t>
+  </si>
+  <si>
+    <t>INE103D08021</t>
+  </si>
+  <si>
+    <t>CRISIL AAA(CE)</t>
+  </si>
+  <si>
+    <t>Altius Telecom Infrastructure Trust. **</t>
+  </si>
+  <si>
+    <t>INE0BWS08019</t>
+  </si>
+  <si>
+    <t>INE883F07314</t>
+  </si>
+  <si>
+    <t>Indostar Capital Finance Ltd.</t>
+  </si>
+  <si>
+    <t>INE896L07975</t>
+  </si>
+  <si>
+    <t>CARE AA-</t>
+  </si>
+  <si>
+    <t>Nexus Select Trust **</t>
+  </si>
+  <si>
+    <t>INE0NDH07050</t>
+  </si>
+  <si>
+    <t>ICRA AAA</t>
+  </si>
+  <si>
+    <t>360 One Prime Ltd.</t>
+  </si>
+  <si>
+    <t>INE248U07EQ0</t>
+  </si>
+  <si>
+    <t>JM Financial Asset Recosntruction Company Ltd. **</t>
+  </si>
+  <si>
+    <t>INE265J07514</t>
+  </si>
+  <si>
+    <t>Hampi Expressways Private Ltd. **</t>
+  </si>
+  <si>
+    <t>INE03ST08010</t>
+  </si>
+  <si>
+    <t>CARE AA+(CE)</t>
   </si>
   <si>
     <t>Indostar Capital Finance Ltd. **</t>
   </si>
   <si>
-    <t>INE896L07876</t>
-  </si>
-  <si>
-    <t>360 One Prime Ltd. **</t>
-  </si>
-  <si>
-    <t>INE248U07FN4</t>
-  </si>
-  <si>
-    <t>ICRA AA</t>
-  </si>
-  <si>
-    <t>Avanse Financial Services Ltd **</t>
-  </si>
-  <si>
-    <t>INE087P07444</t>
-  </si>
-  <si>
-    <t>INE477L07AW0</t>
-  </si>
-  <si>
-    <t>INE729N08113</t>
-  </si>
-  <si>
-    <t>INE165K07019</t>
-  </si>
-  <si>
-    <t>INE729N08097</t>
-  </si>
-  <si>
-    <t>Cholamandalam Investment And Finance Company Ltd.</t>
-  </si>
-  <si>
-    <t>INE121A08PP7</t>
-  </si>
-  <si>
-    <t>LIC Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE115A07QU9</t>
-  </si>
-  <si>
-    <t>JM Financial Asset Recosntruction Company Ltd. **</t>
-  </si>
-  <si>
-    <t>INE265J07514</t>
-  </si>
-  <si>
-    <t>Altius Telecom Infrastructure Trust. **</t>
-  </si>
-  <si>
-    <t>INE0BWS08019</t>
-  </si>
-  <si>
-    <t>INE265J07522</t>
-  </si>
-  <si>
-    <t>Aadhar Housing Finance Ltd. **</t>
-  </si>
-  <si>
-    <t>INE883F07314</t>
-  </si>
-  <si>
-    <t>INE248U07EQ0</t>
-  </si>
-  <si>
-    <t>INE896L07975</t>
-  </si>
-  <si>
-    <t>CARE AA-</t>
-  </si>
-  <si>
-    <t>Hampi Expressways Private Ltd. **</t>
-  </si>
-  <si>
-    <t>INE03ST08010</t>
-  </si>
-  <si>
-    <t>CARE AA+(CE)</t>
+    <t>INE896L07892</t>
+  </si>
+  <si>
+    <t>INE896L07AJ8</t>
   </si>
   <si>
     <t>Aptus Value Housing Finance India Ltd. **</t>
@@ -301,15 +349,6 @@
     <t>INE852O07139</t>
   </si>
   <si>
-    <t>Bharat Sanchar Nigam Ltd. **</t>
-  </si>
-  <si>
-    <t>INE103D08021</t>
-  </si>
-  <si>
-    <t>CRISIL AAA(CE)</t>
-  </si>
-  <si>
     <t>INE201P08183</t>
   </si>
   <si>
@@ -319,9 +358,6 @@
     <t>INE216P07217</t>
   </si>
   <si>
-    <t>CARE AA</t>
-  </si>
-  <si>
     <t>Manappuram Finance Ltd. **</t>
   </si>
   <si>
@@ -337,18 +373,24 @@
     <t>INE017A08250</t>
   </si>
   <si>
+    <t>SIS Ltd. **</t>
+  </si>
+  <si>
+    <t>INE285J07058</t>
+  </si>
+  <si>
     <t>INE105N07217</t>
   </si>
   <si>
     <t>INE105N07225</t>
   </si>
   <si>
+    <t>INE121A08PT9</t>
+  </si>
+  <si>
     <t>INE883F07330</t>
   </si>
   <si>
-    <t>INE896L07892</t>
-  </si>
-  <si>
     <t>INE017A08235</t>
   </si>
   <si>
@@ -361,21 +403,18 @@
     <t>Bahadur Chand Investments Pvt. Ltd. **</t>
   </si>
   <si>
+    <t>INE087M08134</t>
+  </si>
+  <si>
+    <t>INE105N07191</t>
+  </si>
+  <si>
     <t>INE087M08126</t>
   </si>
   <si>
     <t>INE105N07183</t>
   </si>
   <si>
-    <t>INE087M08134</t>
-  </si>
-  <si>
-    <t>INE105N07191</t>
-  </si>
-  <si>
-    <t>INE105N07175</t>
-  </si>
-  <si>
     <t>DME Development Ltd. **</t>
   </si>
   <si>
@@ -388,27 +427,27 @@
     <t>INE0J7Q07074</t>
   </si>
   <si>
+    <t>INE0J7Q07090</t>
+  </si>
+  <si>
     <t>INE0J7Q07082</t>
   </si>
   <si>
-    <t>INE0J7Q07090</t>
+    <t>INE0J7Q07058</t>
+  </si>
+  <si>
+    <t>INE0J7Q07025</t>
+  </si>
+  <si>
+    <t>INE0J7Q07033</t>
   </si>
   <si>
     <t>INE0J7Q07066</t>
   </si>
   <si>
-    <t>INE0J7Q07058</t>
-  </si>
-  <si>
     <t>INE0J7Q07041</t>
   </si>
   <si>
-    <t>INE0J7Q07033</t>
-  </si>
-  <si>
-    <t>INE0J7Q07025</t>
-  </si>
-  <si>
     <t>Sheela Foam Ltd. **</t>
   </si>
   <si>
@@ -418,21 +457,12 @@
     <t>INE916U08038</t>
   </si>
   <si>
-    <t>INE916U08046</t>
+    <t>INE896L07AG4</t>
   </si>
   <si>
     <t>INE916U08020</t>
   </si>
   <si>
-    <t>INE896L07AG4</t>
-  </si>
-  <si>
-    <t>Small Industries Development Bank Of India.</t>
-  </si>
-  <si>
-    <t>INE556F08KJ7</t>
-  </si>
-  <si>
     <t>Rural Electrification Corporation Ltd. **</t>
   </si>
   <si>
@@ -499,6 +529,12 @@
     <t>Units of Real Estate Investment Trust (REITs)</t>
   </si>
   <si>
+    <t>EMBASSY OFFICE PARKS REIT</t>
+  </si>
+  <si>
+    <t>INE041025011</t>
+  </si>
+  <si>
     <t>Brookfield India Real Estate Trust REIT</t>
   </si>
   <si>
@@ -511,10 +547,10 @@
     <t>INE0CCU25019</t>
   </si>
   <si>
-    <t>EMBASSY OFFICE PARKS REIT</t>
-  </si>
-  <si>
-    <t>INE041025011</t>
+    <t>Nexus Select Trust</t>
+  </si>
+  <si>
+    <t>INE0NDH25011</t>
   </si>
   <si>
     <t>Units of an Alternative Investment Fund (AIF)</t>
@@ -538,6 +574,15 @@
     <t>Total Net Assets</t>
   </si>
   <si>
+    <t xml:space="preserve">INTEREST RATE SWAPS (At Notional Value) </t>
+  </si>
+  <si>
+    <t> DBS Bank India Ltd- MD -29-Apr-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
+    <t> Barclays Bank- MD -09-May-2030 (Pay fixed/receive float)</t>
+  </si>
+  <si>
     <t>Non-Convertible debentures / Bonds &amp; Zero Coupon Bonds / Deep Discount Bonds / Certificate of Deposits / Commercial Papers are considered as Traded based on the information provided by external agencies.</t>
   </si>
   <si>
@@ -553,7 +598,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -566,9 +611,6 @@
   </si>
   <si>
     <t>Benchmark Riskometer</t>
-  </si>
-  <si>
-    <t>Benchmark name - NIFTY Medium Duration Debt Index A-III</t>
   </si>
 </sst>
 </file>
@@ -656,7 +698,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -742,6 +784,14 @@
         <color auto="1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -768,7 +818,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -846,6 +896,9 @@
       <protection/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyProtection="1">
       <protection/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -946,13 +999,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>148</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>149</xdr:row>
+      <xdr:row>158</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -970,8 +1023,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="27336750"/>
-          <a:ext cx="3914775" cy="1905000"/>
+          <a:off x="666750" y="29041725"/>
+          <a:ext cx="4333875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -985,13 +1038,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>154</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>164</xdr:row>
+      <xdr:row>173</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1009,8 +1062,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="30194250"/>
-          <a:ext cx="3914775" cy="1905000"/>
+          <a:off x="666750" y="31899225"/>
+          <a:ext cx="4333875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
         <a:ln w="9525" cmpd="sng">
@@ -1343,19 +1396,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J153"/>
+  <dimension ref="B1:J161"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="22" width="10.0" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="22" width="58.714285714285715" collapsed="true"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="22" width="17.0" collapsed="true"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="22" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="22" width="47.142857142857146" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="22" width="12.285714285714286" collapsed="true"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="22" width="38.714285714285715" collapsed="true"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="22" width="11.714285714285714" collapsed="true"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="22" width="29.714285714285715" collapsed="true"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="22" width="26.714285714285715" collapsed="true"/>
+    <col min="1" max="1" customWidth="true" style="23" width="10.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="23" width="65.0" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="23" width="17.0" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="23" width="9.714285714285714" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="23" width="47.142857142857146" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="23" width="12.285714285714286" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="23" width="38.714285714285715" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="23" width="11.714285714285714" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="23" width="29.714285714285715" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="23" width="26.714285714285715" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" customHeight="1">
@@ -1443,10 +1496,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>514775.6400000002</v>
+        <v>515514.6100000001</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9038913006086002</v>
+        <v>0.8992720193437999</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1480,10 +1533,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>514775.6400000002</v>
+        <v>515514.6100000001</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9038913006086002</v>
+        <v>0.8992720193437999</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1517,10 +1570,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>158414.52000000002</v>
+        <v>149494.88000000003</v>
       </c>
       <c r="H9" s="10">
-        <v>0.2781590568631</v>
+        <v>0.26078128536360007</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1543,16 +1596,16 @@
         <v>17</v>
       </c>
       <c r="F10" s="15">
-        <v>148573350</v>
+        <v>103247750</v>
       </c>
       <c r="G10" s="16">
-        <v>152148.62</v>
+        <v>108841.71</v>
       </c>
       <c r="H10" s="17">
-        <v>0.2671568025598</v>
+        <v>0.1898652384284</v>
       </c>
       <c r="I10" s="16">
-        <v>6.86</v>
+        <v>6.39</v>
       </c>
       <c r="J10" s="11" t="s">
         <v>13</v>
@@ -1566,22 +1619,22 @@
         <v>18</v>
       </c>
       <c r="D11" s="14">
-        <v>6.79</v>
+        <v>7.34</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="15">
-        <v>4370700</v>
+        <v>18801500</v>
       </c>
       <c r="G11" s="16">
-        <v>4399.53</v>
+        <v>20012.96</v>
       </c>
       <c r="H11" s="17">
-        <v>0.0077251069879</v>
+        <v>0.0349109309478</v>
       </c>
       <c r="I11" s="16">
-        <v>6.81</v>
+        <v>6.98</v>
       </c>
       <c r="J11" s="11" t="s">
         <v>13</v>
@@ -1595,22 +1648,22 @@
         <v>19</v>
       </c>
       <c r="D12" s="14">
-        <v>7.26</v>
+        <v>6.79</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="15">
-        <v>1334300</v>
+        <v>9180250</v>
       </c>
       <c r="G12" s="16">
-        <v>1375.95</v>
+        <v>9510.09</v>
       </c>
       <c r="H12" s="17">
-        <v>0.0024160219296</v>
+        <v>0.0165895547334</v>
       </c>
       <c r="I12" s="16">
-        <v>6.86</v>
+        <v>6.37</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>13</v>
@@ -1624,19 +1677,19 @@
         <v>20</v>
       </c>
       <c r="D13" s="14">
-        <v>6.92</v>
+        <v>7.09</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="15">
-        <v>281800</v>
+        <v>4000000</v>
       </c>
       <c r="G13" s="16">
-        <v>284.28</v>
+        <v>4133.25</v>
       </c>
       <c r="H13" s="17">
-        <v>0.0004991654596</v>
+        <v>0.0072101081169</v>
       </c>
       <c r="I13" s="16">
         <v>6.94</v>
@@ -1647,28 +1700,28 @@
     </row>
     <row r="14" spans="2:10" ht="15" customHeight="1">
       <c r="B14" s="12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D14" s="14">
-        <v>7.18</v>
+        <v>7.140000000000001</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="15">
-        <v>200650</v>
+        <v>2000000</v>
       </c>
       <c r="G14" s="16">
-        <v>206.14</v>
+        <v>2075.51</v>
       </c>
       <c r="H14" s="17">
-        <v>0.0003619599262</v>
+        <v>0.0036205531961</v>
       </c>
       <c r="I14" s="16">
-        <v>6.87</v>
+        <v>6.82</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>13</v>
@@ -1676,36 +1729,57 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>13</v>
+        <v>21</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="14">
+        <v>7.12</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="15">
+        <v>1653600</v>
+      </c>
+      <c r="G15" s="16">
+        <v>1709.23</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0.0029816084429</v>
+      </c>
+      <c r="I15" s="16">
+        <v>6.83</v>
       </c>
       <c r="J15" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
-      <c r="B16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="9">
-        <v>356361.12000000017</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0.6257322437455001</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>13</v>
+      <c r="B16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="14">
+        <v>7.32</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="15">
+        <v>1381400</v>
+      </c>
+      <c r="G16" s="16">
+        <v>1449.95</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0.0025293162194</v>
+      </c>
+      <c r="I16" s="16">
+        <v>6.81</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>13</v>
@@ -1713,28 +1787,28 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D17" s="14">
-        <v>8.40</v>
+        <v>7.13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F17" s="15">
-        <v>15000</v>
+        <v>1331200</v>
       </c>
       <c r="G17" s="16">
-        <v>15065.07</v>
+        <v>1375.06</v>
       </c>
       <c r="H17" s="17">
-        <v>0.0264526614276</v>
+        <v>0.0023986768928</v>
       </c>
       <c r="I17" s="16">
-        <v>8.22</v>
+        <v>6.75</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>13</v>
@@ -1742,28 +1816,28 @@
     </row>
     <row r="18" spans="2:10" ht="15" customHeight="1">
       <c r="B18" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D18" s="14">
-        <v>8.05</v>
+        <v>7.29</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F18" s="15">
-        <v>15000</v>
+        <v>288800</v>
       </c>
       <c r="G18" s="16">
-        <v>14942.46</v>
+        <v>301.47</v>
       </c>
       <c r="H18" s="17">
-        <v>0.0262373713016</v>
+        <v>0.0005258891414</v>
       </c>
       <c r="I18" s="16">
-        <v>8.55</v>
+        <v>6.88</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>13</v>
@@ -1771,28 +1845,28 @@
     </row>
     <row r="19" spans="2:10" ht="15" customHeight="1">
       <c r="B19" s="12" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>30</v>
       </c>
       <c r="D19" s="14">
-        <v>7.96</v>
+        <v>6.92</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F19" s="15">
-        <v>12400</v>
+        <v>81800</v>
       </c>
       <c r="G19" s="16">
-        <v>12539.69</v>
+        <v>85.65</v>
       </c>
       <c r="H19" s="17">
-        <v>0.0220183626081</v>
+        <v>0.0001494092445</v>
       </c>
       <c r="I19" s="16">
-        <v>7.84</v>
+        <v>6.52</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>13</v>
@@ -1800,57 +1874,36 @@
     </row>
     <row r="20" spans="2:10" ht="15" customHeight="1">
       <c r="B20" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" s="14">
-        <v>8.60</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="15">
-        <v>12500</v>
-      </c>
-      <c r="G20" s="16">
-        <v>12471.16</v>
-      </c>
-      <c r="H20" s="17">
-        <v>0.0218980312132</v>
-      </c>
-      <c r="I20" s="16">
-        <v>9.03</v>
+        <v>13</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
-      <c r="B21" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" s="14">
-        <v>9.50</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="15">
-        <v>110</v>
-      </c>
-      <c r="G21" s="16">
-        <v>11236.58</v>
-      </c>
-      <c r="H21" s="17">
-        <v>0.0197302399752</v>
-      </c>
-      <c r="I21" s="16">
-        <v>8.64</v>
+      <c r="B21" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="9">
+        <v>366019.73000000004</v>
+      </c>
+      <c r="H21" s="10">
+        <v>0.6384907339801998</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>13</v>
@@ -1858,28 +1911,28 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D22" s="14">
-        <v>9.25</v>
+        <v>9.40</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="F22" s="15">
-        <v>11000</v>
+        <v>17000</v>
       </c>
       <c r="G22" s="16">
-        <v>10911.08</v>
+        <v>17078.61</v>
       </c>
       <c r="H22" s="17">
-        <v>0.0191586965775</v>
+        <v>0.0297922033719</v>
       </c>
       <c r="I22" s="16">
-        <v>9.77</v>
+        <v>9.06</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>13</v>
@@ -1887,28 +1940,28 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D23" s="14">
-        <v>8.32</v>
+        <v>8.40</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F23" s="15">
-        <v>10500</v>
+        <v>15000</v>
       </c>
       <c r="G23" s="16">
-        <v>10616.06</v>
+        <v>15417.27</v>
       </c>
       <c r="H23" s="17">
-        <v>0.0186406728196</v>
+        <v>0.0268941350192</v>
       </c>
       <c r="I23" s="16">
-        <v>7.99</v>
+        <v>7.22</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>13</v>
@@ -1916,28 +1969,28 @@
     </row>
     <row r="24" spans="2:10" ht="15" customHeight="1">
       <c r="B24" s="12" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D24" s="14">
-        <v>8.50</v>
+        <v>8.05</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F24" s="15">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="G24" s="16">
-        <v>10082.38</v>
+        <v>15231.56</v>
       </c>
       <c r="H24" s="17">
-        <v>0.0177035874725</v>
+        <v>0.0265701794931</v>
       </c>
       <c r="I24" s="16">
-        <v>8.04</v>
+        <v>7.76</v>
       </c>
       <c r="J24" s="11" t="s">
         <v>13</v>
@@ -1945,28 +1998,28 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D25" s="14">
-        <v>8.50</v>
+        <v>8.60</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F25" s="15">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="G25" s="16">
-        <v>9984.3</v>
+        <v>15143.31</v>
       </c>
       <c r="H25" s="17">
-        <v>0.0175313694189</v>
+        <v>0.0264162347664</v>
       </c>
       <c r="I25" s="16">
-        <v>9.2</v>
+        <v>7.93</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>13</v>
@@ -1974,28 +2027,28 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D26" s="14">
-        <v>8.35</v>
+        <v>8.60</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F26" s="15">
-        <v>10000</v>
+        <v>12500</v>
       </c>
       <c r="G26" s="16">
-        <v>9977.40</v>
+        <v>12641.86</v>
       </c>
       <c r="H26" s="17">
-        <v>0.0175192537524</v>
+        <v>0.0220526649487</v>
       </c>
       <c r="I26" s="16">
-        <v>8.48</v>
+        <v>8.05</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>13</v>
@@ -2003,28 +2056,28 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D27" s="14">
-        <v>8.45</v>
+        <v>9.50</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="F27" s="15">
-        <v>10000</v>
+        <v>110</v>
       </c>
       <c r="G27" s="16">
-        <v>9932.45</v>
+        <v>11357.29</v>
       </c>
       <c r="H27" s="17">
-        <v>0.0174403263308</v>
+        <v>0.0198118402747</v>
       </c>
       <c r="I27" s="16">
-        <v>8.74</v>
+        <v>8.11</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>13</v>
@@ -2032,28 +2085,28 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="14">
+        <v>9.25</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="14">
-        <v>8.32</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="F28" s="15">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="G28" s="16">
-        <v>9900.17</v>
+        <v>10973.39</v>
       </c>
       <c r="H28" s="17">
-        <v>0.0173836460823</v>
+        <v>0.0191421589087</v>
       </c>
       <c r="I28" s="16">
-        <v>8.71</v>
+        <v>9.41</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>13</v>
@@ -2061,28 +2114,28 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D29" s="14">
-        <v>9.99</v>
+        <v>8.32</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F29" s="15">
-        <v>90</v>
+        <v>10500</v>
       </c>
       <c r="G29" s="16">
-        <v>8935.73</v>
+        <v>10848.59</v>
       </c>
       <c r="H29" s="17">
-        <v>0.0156901919671</v>
+        <v>0.0189244557712</v>
       </c>
       <c r="I29" s="16">
-        <v>10.86</v>
+        <v>7.26</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>13</v>
@@ -2090,28 +2143,28 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D30" s="14">
-        <v>8.28</v>
+        <v>7.96</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F30" s="15">
-        <v>8237</v>
+        <v>9900</v>
       </c>
       <c r="G30" s="16">
-        <v>8165.04</v>
+        <v>10259.96</v>
       </c>
       <c r="H30" s="17">
-        <v>0.0143369422553</v>
+        <v>0.0178976400836</v>
       </c>
       <c r="I30" s="16">
-        <v>9.04</v>
+        <v>6.98</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>13</v>
@@ -2119,28 +2172,28 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D31" s="14">
-        <v>8.55</v>
+        <v>8.50</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F31" s="15">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="G31" s="16">
-        <v>8101.22</v>
+        <v>10166.63</v>
       </c>
       <c r="H31" s="17">
-        <v>0.0142248811197</v>
+        <v>0.0177348337228</v>
       </c>
       <c r="I31" s="16">
-        <v>8.18</v>
+        <v>7.40</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>13</v>
@@ -2148,28 +2201,28 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>62</v>
-      </c>
       <c r="D32" s="14">
-        <v>8.73</v>
+        <v>8.45</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="F32" s="15">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="G32" s="16">
-        <v>7529.28</v>
+        <v>10108.66</v>
       </c>
       <c r="H32" s="17">
-        <v>0.0132206152798</v>
+        <v>0.0176337099177</v>
       </c>
       <c r="I32" s="16">
-        <v>8.50</v>
+        <v>7.85</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>13</v>
@@ -2177,28 +2230,28 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D33" s="14">
-        <v>8.73</v>
+        <v>8.35</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="F33" s="15">
-        <v>7500</v>
+        <v>10000</v>
       </c>
       <c r="G33" s="16">
-        <v>7524.35</v>
+        <v>10098.54</v>
       </c>
       <c r="H33" s="17">
-        <v>0.0132119587239</v>
+        <v>0.0176160564261</v>
       </c>
       <c r="I33" s="16">
-        <v>8.53</v>
+        <v>7.66</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>13</v>
@@ -2206,28 +2259,28 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="14">
+        <v>9.99</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D34" s="14">
-        <v>9.950000000000001</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>34</v>
-      </c>
       <c r="F34" s="15">
-        <v>7500</v>
+        <v>90</v>
       </c>
       <c r="G34" s="16">
-        <v>7515.77</v>
+        <v>9020.46</v>
       </c>
       <c r="H34" s="17">
-        <v>0.013196893156</v>
+        <v>0.0157354362462</v>
       </c>
       <c r="I34" s="16">
-        <v>9.50</v>
+        <v>9.93</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>13</v>
@@ -2235,28 +2288,28 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>68</v>
-      </c>
       <c r="D35" s="14">
-        <v>9.50</v>
+        <v>8.55</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="F35" s="15">
-        <v>7500</v>
+        <v>8000</v>
       </c>
       <c r="G35" s="16">
-        <v>7511.60</v>
+        <v>8324.24</v>
       </c>
       <c r="H35" s="17">
-        <v>0.0131895710793</v>
+        <v>0.0145209388233</v>
       </c>
       <c r="I35" s="16">
-        <v>9.3</v>
+        <v>7.37</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>13</v>
@@ -2264,28 +2317,28 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D36" s="14">
-        <v>9.40</v>
+        <v>8.28</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F36" s="15">
-        <v>7500</v>
+        <v>8237</v>
       </c>
       <c r="G36" s="16">
-        <v>7496.03</v>
+        <v>8274.89</v>
       </c>
       <c r="H36" s="17">
-        <v>0.0131622318144</v>
+        <v>0.0144348518855</v>
       </c>
       <c r="I36" s="16">
-        <v>9.66</v>
+        <v>8.05</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>13</v>
@@ -2293,28 +2346,28 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D37" s="14">
-        <v>8.50</v>
+        <v>8.73</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F37" s="15">
         <v>7500</v>
       </c>
       <c r="G37" s="16">
-        <v>7471.22</v>
+        <v>7651.37</v>
       </c>
       <c r="H37" s="17">
-        <v>0.0131186680919</v>
+        <v>0.0133471735178</v>
       </c>
       <c r="I37" s="16">
-        <v>9.25</v>
+        <v>7.61</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>13</v>
@@ -2322,28 +2375,28 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D38" s="14">
-        <v>9.38</v>
+        <v>8.73</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F38" s="15">
-        <v>70</v>
+        <v>7500</v>
       </c>
       <c r="G38" s="16">
-        <v>7216.78</v>
+        <v>7622.84</v>
       </c>
       <c r="H38" s="17">
-        <v>0.0126718985001</v>
+        <v>0.0132974053246</v>
       </c>
       <c r="I38" s="16">
-        <v>8.61</v>
+        <v>7.60</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>13</v>
@@ -2351,28 +2404,28 @@
     </row>
     <row r="39" spans="2:10" ht="15" customHeight="1">
       <c r="B39" s="12" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>74</v>
       </c>
       <c r="D39" s="14">
-        <v>9.99</v>
+        <v>9.50</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="F39" s="15">
-        <v>60</v>
+        <v>7500</v>
       </c>
       <c r="G39" s="16">
-        <v>5983.73</v>
+        <v>7561.42</v>
       </c>
       <c r="H39" s="17">
-        <v>0.0105067937795</v>
+        <v>0.0131902632837</v>
       </c>
       <c r="I39" s="16">
-        <v>10.87</v>
+        <v>8.63</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>13</v>
@@ -2380,28 +2433,28 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D40" s="14">
-        <v>9.35</v>
+        <v>9.40</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="F40" s="15">
-        <v>50</v>
+        <v>7500</v>
       </c>
       <c r="G40" s="16">
-        <v>5107.4</v>
+        <v>7532.07</v>
       </c>
       <c r="H40" s="17">
-        <v>0.0089680514578</v>
+        <v>0.0131390646693</v>
       </c>
       <c r="I40" s="16">
-        <v>8.64</v>
+        <v>9.21</v>
       </c>
       <c r="J40" s="11" t="s">
         <v>13</v>
@@ -2409,28 +2462,28 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D41" s="14">
-        <v>9.10</v>
+        <v>9.38</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F41" s="15">
-        <v>5000</v>
+        <v>70</v>
       </c>
       <c r="G41" s="16">
-        <v>5019.15</v>
+        <v>7318.35</v>
       </c>
       <c r="H41" s="17">
-        <v>0.0088130938392</v>
+        <v>0.0127662480463</v>
       </c>
       <c r="I41" s="16">
-        <v>9</v>
+        <v>8.21</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>13</v>
@@ -2438,28 +2491,28 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D42" s="14">
-        <v>7.75</v>
+        <v>8.10</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="F42" s="15">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="G42" s="16">
-        <v>5013.25</v>
+        <v>7058.02</v>
       </c>
       <c r="H42" s="17">
-        <v>0.0088027340664</v>
+        <v>0.0123121241859</v>
       </c>
       <c r="I42" s="16">
-        <v>7.66</v>
+        <v>7.81</v>
       </c>
       <c r="J42" s="11" t="s">
         <v>13</v>
@@ -2467,28 +2520,28 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D43" s="14">
-        <v>10.200000000000001</v>
+        <v>9.10</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F43" s="15">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="G43" s="16">
-        <v>5012.96</v>
+        <v>5642.81</v>
       </c>
       <c r="H43" s="17">
-        <v>0.0088022248572</v>
+        <v>0.009843408984</v>
       </c>
       <c r="I43" s="16">
-        <v>9.88</v>
+        <v>8.53</v>
       </c>
       <c r="J43" s="11" t="s">
         <v>13</v>
@@ -2496,28 +2549,28 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D44" s="14">
-        <v>8.40</v>
+        <v>9.35</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="F44" s="15">
-        <v>5000</v>
+        <v>50</v>
       </c>
       <c r="G44" s="16">
-        <v>5010.4</v>
+        <v>5171.64</v>
       </c>
       <c r="H44" s="17">
-        <v>0.0087977297693</v>
+        <v>0.0090214924192</v>
       </c>
       <c r="I44" s="16">
-        <v>8.50</v>
+        <v>8.11</v>
       </c>
       <c r="J44" s="11" t="s">
         <v>13</v>
@@ -2525,28 +2578,28 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D45" s="14">
-        <v>10.200000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F45" s="15">
         <v>5000</v>
       </c>
       <c r="G45" s="16">
-        <v>5009.13</v>
+        <v>5095.50</v>
       </c>
       <c r="H45" s="17">
-        <v>0.0087954997843</v>
+        <v>0.0088886725724</v>
       </c>
       <c r="I45" s="16">
-        <v>9.77</v>
+        <v>7.41</v>
       </c>
       <c r="J45" s="11" t="s">
         <v>13</v>
@@ -2554,28 +2607,28 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D46" s="14">
-        <v>8.50</v>
+        <v>6.79</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="F46" s="15">
-        <v>5000</v>
+        <v>510</v>
       </c>
       <c r="G46" s="16">
-        <v>5004.11</v>
+        <v>5095.02</v>
       </c>
       <c r="H46" s="17">
-        <v>0.008786685198</v>
+        <v>0.0088878352526</v>
       </c>
       <c r="I46" s="16">
-        <v>8.38</v>
+        <v>6.93</v>
       </c>
       <c r="J46" s="11" t="s">
         <v>13</v>
@@ -2583,28 +2636,28 @@
     </row>
     <row r="47" spans="2:10" ht="15" customHeight="1">
       <c r="B47" s="12" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="D47" s="14">
-        <v>9.41</v>
+        <v>8.40</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="F47" s="15">
-        <v>500000</v>
+        <v>5000</v>
       </c>
       <c r="G47" s="16">
-        <v>5002.98</v>
+        <v>5059.87</v>
       </c>
       <c r="H47" s="17">
-        <v>0.0087847010381</v>
+        <v>0.0088265190244</v>
       </c>
       <c r="I47" s="16">
-        <v>9.34</v>
+        <v>7.40</v>
       </c>
       <c r="J47" s="11" t="s">
         <v>13</v>
@@ -2612,28 +2665,28 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D48" s="14">
-        <v>9.950000000000001</v>
+        <v>8.50</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="F48" s="15">
         <v>5000</v>
       </c>
       <c r="G48" s="16">
-        <v>4990.92</v>
+        <v>5053.19</v>
       </c>
       <c r="H48" s="17">
-        <v>0.0087635249602</v>
+        <v>0.0088148663244</v>
       </c>
       <c r="I48" s="16">
-        <v>10.44</v>
+        <v>7.50</v>
       </c>
       <c r="J48" s="11" t="s">
         <v>13</v>
@@ -2641,28 +2694,28 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D49" s="14">
-        <v>8.2</v>
+        <v>9.950000000000001</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F49" s="15">
         <v>5000</v>
       </c>
       <c r="G49" s="16">
-        <v>4962.51</v>
+        <v>5046.97</v>
       </c>
       <c r="H49" s="17">
-        <v>0.0087136400203</v>
+        <v>0.0088040160558</v>
       </c>
       <c r="I49" s="16">
-        <v>8.36</v>
+        <v>9.60</v>
       </c>
       <c r="J49" s="11" t="s">
         <v>13</v>
@@ -2670,28 +2723,28 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C50" s="13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D50" s="14">
-        <v>8.75</v>
+        <v>7.19</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F50" s="15">
         <v>5000</v>
       </c>
       <c r="G50" s="16">
-        <v>4951.95</v>
+        <v>5030.46</v>
       </c>
       <c r="H50" s="17">
-        <v>0.0086950977829</v>
+        <v>0.0087752157449</v>
       </c>
       <c r="I50" s="16">
-        <v>9.90</v>
+        <v>7.08</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>13</v>
@@ -2699,28 +2752,28 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D51" s="14">
-        <v>6.79</v>
+        <v>9.41</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="F51" s="15">
-        <v>510</v>
+        <v>500000</v>
       </c>
       <c r="G51" s="16">
-        <v>4948</v>
+        <v>5019.38</v>
       </c>
       <c r="H51" s="17">
-        <v>0.0086881620028</v>
+        <v>0.0087558876138</v>
       </c>
       <c r="I51" s="16">
-        <v>7.58</v>
+        <v>8.50</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>13</v>
@@ -2728,28 +2781,28 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>48</v>
+        <v>101</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="D52" s="14">
-        <v>8.55</v>
+        <v>10.200000000000001</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="F52" s="15">
-        <v>490</v>
+        <v>5000</v>
       </c>
       <c r="G52" s="16">
-        <v>4893.63</v>
+        <v>5014.34</v>
       </c>
       <c r="H52" s="17">
-        <v>0.0085926940626</v>
+        <v>0.0087470957564</v>
       </c>
       <c r="I52" s="16">
-        <v>8.47</v>
+        <v>8.35</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>13</v>
@@ -2757,28 +2810,28 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D53" s="14">
-        <v>8.75</v>
+        <v>8.2</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F53" s="15">
-        <v>450</v>
+        <v>5000</v>
       </c>
       <c r="G53" s="16">
-        <v>4528.24</v>
+        <v>5004.41</v>
       </c>
       <c r="H53" s="17">
-        <v>0.0079511080654</v>
+        <v>0.0087297737038</v>
       </c>
       <c r="I53" s="16">
-        <v>8.33</v>
+        <v>7.42</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>13</v>
@@ -2786,28 +2839,28 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D54" s="14">
-        <v>9.10</v>
+        <v>9.950000000000001</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="F54" s="15">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G54" s="16">
-        <v>3998.80</v>
+        <v>5002.98</v>
       </c>
       <c r="H54" s="17">
-        <v>0.0070214677075</v>
+        <v>0.0087272791887</v>
       </c>
       <c r="I54" s="16">
-        <v>9.05</v>
+        <v>9.04</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>13</v>
@@ -2818,25 +2871,25 @@
         <v>93</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D55" s="14">
-        <v>8.75</v>
+        <v>9.60</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F55" s="15">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G55" s="16">
-        <v>3955.76</v>
+        <v>4990.83</v>
       </c>
       <c r="H55" s="17">
-        <v>0.0069458940429</v>
+        <v>0.0087060845323</v>
       </c>
       <c r="I55" s="16">
-        <v>9.88</v>
+        <v>9.76</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>13</v>
@@ -2844,28 +2897,28 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D56" s="14">
-        <v>8.24</v>
+        <v>8.75</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="F56" s="15">
-        <v>380</v>
+        <v>5000</v>
       </c>
       <c r="G56" s="16">
-        <v>3781.11</v>
+        <v>4979.16</v>
       </c>
       <c r="H56" s="17">
-        <v>0.006639227209</v>
+        <v>0.0086857271956</v>
       </c>
       <c r="I56" s="16">
-        <v>8.77</v>
+        <v>9.55</v>
       </c>
       <c r="J56" s="11" t="s">
         <v>13</v>
@@ -2873,28 +2926,28 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D57" s="14">
-        <v>8.28</v>
+        <v>8.05</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F57" s="15">
-        <v>3094</v>
+        <v>490</v>
       </c>
       <c r="G57" s="16">
-        <v>3066.05</v>
+        <v>4900.07</v>
       </c>
       <c r="H57" s="17">
-        <v>0.0053836578635</v>
+        <v>0.0085477613211</v>
       </c>
       <c r="I57" s="16">
-        <v>8.93</v>
+        <v>7.20</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>13</v>
@@ -2902,28 +2955,28 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D58" s="14">
-        <v>8.28</v>
+        <v>8.75</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="F58" s="15">
-        <v>3000</v>
+        <v>450</v>
       </c>
       <c r="G58" s="16">
-        <v>2968.69</v>
+        <v>4573.78</v>
       </c>
       <c r="H58" s="17">
-        <v>0.0052127040533</v>
+        <v>0.0079785757704</v>
       </c>
       <c r="I58" s="16">
-        <v>8.91</v>
+        <v>7.43</v>
       </c>
       <c r="J58" s="11" t="s">
         <v>13</v>
@@ -2931,28 +2984,28 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="D59" s="14">
-        <v>8.65</v>
+        <v>9.10</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="F59" s="15">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="G59" s="16">
-        <v>2519.3</v>
+        <v>4039.95</v>
       </c>
       <c r="H59" s="17">
-        <v>0.0044236229857</v>
+        <v>0.0070473540886</v>
       </c>
       <c r="I59" s="16">
-        <v>8.33</v>
+        <v>8.15</v>
       </c>
       <c r="J59" s="11" t="s">
         <v>13</v>
@@ -2960,28 +3013,28 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D60" s="14">
-        <v>9.950000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="F60" s="15">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="G60" s="16">
-        <v>2507.48</v>
+        <v>3979.35</v>
       </c>
       <c r="H60" s="17">
-        <v>0.0044028683223</v>
+        <v>0.006941642469</v>
       </c>
       <c r="I60" s="16">
-        <v>9.50</v>
+        <v>9.55</v>
       </c>
       <c r="J60" s="11" t="s">
         <v>13</v>
@@ -2989,28 +3042,28 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D61" s="14">
-        <v>8.700000000000001</v>
+        <v>8.24</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="F61" s="15">
-        <v>250</v>
+        <v>380</v>
       </c>
       <c r="G61" s="16">
-        <v>2499.7</v>
+        <v>3806.76</v>
       </c>
       <c r="H61" s="17">
-        <v>0.0043892074693</v>
+        <v>0.006640573683</v>
       </c>
       <c r="I61" s="16">
-        <v>8.65</v>
+        <v>7.49</v>
       </c>
       <c r="J61" s="11" t="s">
         <v>13</v>
@@ -3018,28 +3071,28 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D62" s="14">
-        <v>8.92</v>
+        <v>8.50</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="F62" s="15">
-        <v>2500</v>
+        <v>3750</v>
       </c>
       <c r="G62" s="16">
-        <v>2495.90</v>
+        <v>3777.88</v>
       </c>
       <c r="H62" s="17">
-        <v>0.0043825350733</v>
+        <v>0.0065901949441</v>
       </c>
       <c r="I62" s="16">
-        <v>9.35</v>
+        <v>8.37</v>
       </c>
       <c r="J62" s="11" t="s">
         <v>13</v>
@@ -3047,28 +3100,28 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D63" s="14">
-        <v>9.25</v>
+        <v>8.28</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="F63" s="15">
-        <v>2500</v>
+        <v>3094</v>
       </c>
       <c r="G63" s="16">
-        <v>2493.14</v>
+        <v>3115.64</v>
       </c>
       <c r="H63" s="17">
-        <v>0.0043776888067</v>
+        <v>0.0054349727825</v>
       </c>
       <c r="I63" s="16">
-        <v>9.91</v>
+        <v>8.01</v>
       </c>
       <c r="J63" s="11" t="s">
         <v>13</v>
@@ -3076,28 +3129,28 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D64" s="14">
         <v>8.28</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F64" s="15">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="G64" s="16">
-        <v>2488.93</v>
+        <v>3026.39</v>
       </c>
       <c r="H64" s="17">
-        <v>0.0043702964942</v>
+        <v>0.0052792836397</v>
       </c>
       <c r="I64" s="16">
-        <v>9.16</v>
+        <v>8.01</v>
       </c>
       <c r="J64" s="11" t="s">
         <v>13</v>
@@ -3105,28 +3158,28 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D65" s="14">
-        <v>9.25</v>
+        <v>9.05</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="F65" s="15">
         <v>2500</v>
       </c>
       <c r="G65" s="16">
-        <v>2485.91</v>
+        <v>2558.99</v>
       </c>
       <c r="H65" s="17">
-        <v>0.0043649936953</v>
+        <v>0.0044639435239</v>
       </c>
       <c r="I65" s="16">
-        <v>9.8</v>
+        <v>8.56</v>
       </c>
       <c r="J65" s="11" t="s">
         <v>13</v>
@@ -3134,28 +3187,28 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D66" s="14">
-        <v>8.28</v>
+        <v>8.65</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F66" s="15">
         <v>2500</v>
       </c>
       <c r="G66" s="16">
-        <v>2482.93</v>
+        <v>2545.81</v>
       </c>
       <c r="H66" s="17">
-        <v>0.0043597611321</v>
+        <v>0.0044409521188</v>
       </c>
       <c r="I66" s="16">
-        <v>9.10</v>
+        <v>7.72</v>
       </c>
       <c r="J66" s="11" t="s">
         <v>13</v>
@@ -3163,28 +3216,28 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>58</v>
+        <v>117</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D67" s="14">
-        <v>8.28</v>
+        <v>8.700000000000001</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F67" s="15">
-        <v>2000</v>
+        <v>250</v>
       </c>
       <c r="G67" s="16">
-        <v>1997.71</v>
+        <v>2524.71</v>
       </c>
       <c r="H67" s="17">
-        <v>0.0035077663934</v>
+        <v>0.0044041449377</v>
       </c>
       <c r="I67" s="16">
-        <v>8.78</v>
+        <v>7.52</v>
       </c>
       <c r="J67" s="11" t="s">
         <v>13</v>
@@ -3192,28 +3245,28 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D68" s="14">
-        <v>9.54</v>
+        <v>8.92</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F68" s="15">
-        <v>165</v>
+        <v>2500</v>
       </c>
       <c r="G68" s="16">
-        <v>1755.03</v>
+        <v>2519.87</v>
       </c>
       <c r="H68" s="17">
-        <v>0.0030816461115</v>
+        <v>0.0043957019635</v>
       </c>
       <c r="I68" s="16">
-        <v>9.47</v>
+        <v>8.48</v>
       </c>
       <c r="J68" s="11" t="s">
         <v>13</v>
@@ -3221,28 +3274,28 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D69" s="14">
-        <v>9.54</v>
+        <v>9.25</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F69" s="15">
-        <v>165</v>
+        <v>2500</v>
       </c>
       <c r="G69" s="16">
-        <v>1753.08</v>
+        <v>2511.43</v>
       </c>
       <c r="H69" s="17">
-        <v>0.0030782221188</v>
+        <v>0.004380979091</v>
       </c>
       <c r="I69" s="16">
-        <v>9.43</v>
+        <v>8.40</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>13</v>
@@ -3250,28 +3303,28 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="D70" s="14">
-        <v>9.54</v>
+        <v>8.28</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F70" s="15">
-        <v>165</v>
+        <v>2500</v>
       </c>
       <c r="G70" s="16">
-        <v>1742.52</v>
+        <v>2507.8</v>
       </c>
       <c r="H70" s="17">
-        <v>0.0030596798813</v>
+        <v>0.0043746468603</v>
       </c>
       <c r="I70" s="16">
-        <v>9.28</v>
+        <v>8.02</v>
       </c>
       <c r="J70" s="11" t="s">
         <v>13</v>
@@ -3279,28 +3332,28 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D71" s="14">
-        <v>9.54</v>
+        <v>9.25</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F71" s="15">
-        <v>165</v>
+        <v>2500</v>
       </c>
       <c r="G71" s="16">
-        <v>1740.65</v>
+        <v>2506.29</v>
       </c>
       <c r="H71" s="17">
-        <v>0.0030563963601</v>
+        <v>0.0043720127919</v>
       </c>
       <c r="I71" s="16">
-        <v>9.36</v>
+        <v>8</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>13</v>
@@ -3308,28 +3361,28 @@
     </row>
     <row r="72" spans="2:10" ht="15" customHeight="1">
       <c r="B72" s="12" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D72" s="14">
-        <v>9.54</v>
+        <v>8.28</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F72" s="15">
-        <v>165</v>
+        <v>2500</v>
       </c>
       <c r="G72" s="16">
-        <v>1736.15</v>
+        <v>2503.06</v>
       </c>
       <c r="H72" s="17">
-        <v>0.0030484948385</v>
+        <v>0.0043663783277</v>
       </c>
       <c r="I72" s="16">
-        <v>9.45</v>
+        <v>7.79</v>
       </c>
       <c r="J72" s="11" t="s">
         <v>13</v>
@@ -3337,28 +3390,28 @@
     </row>
     <row r="73" spans="2:10" ht="15" customHeight="1">
       <c r="B73" s="12" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D73" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E73" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F73" s="15">
         <v>165</v>
       </c>
       <c r="G73" s="16">
-        <v>1730.03</v>
+        <v>1756.45</v>
       </c>
       <c r="H73" s="17">
-        <v>0.0030377487691</v>
+        <v>0.0030639797742</v>
       </c>
       <c r="I73" s="16">
-        <v>9.3</v>
+        <v>8.95</v>
       </c>
       <c r="J73" s="11" t="s">
         <v>13</v>
@@ -3366,28 +3419,28 @@
     </row>
     <row r="74" spans="2:10" ht="15" customHeight="1">
       <c r="B74" s="12" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="D74" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E74" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F74" s="15">
         <v>165</v>
       </c>
       <c r="G74" s="16">
-        <v>1723.02</v>
+        <v>1747.96</v>
       </c>
       <c r="H74" s="17">
-        <v>0.0030254399543</v>
+        <v>0.003049169681</v>
       </c>
       <c r="I74" s="16">
-        <v>9.24</v>
+        <v>8.93</v>
       </c>
       <c r="J74" s="11" t="s">
         <v>13</v>
@@ -3395,28 +3448,28 @@
     </row>
     <row r="75" spans="2:10" ht="15" customHeight="1">
       <c r="B75" s="12" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D75" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E75" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F75" s="15">
         <v>165</v>
       </c>
       <c r="G75" s="16">
-        <v>1715.37</v>
+        <v>1745.17</v>
       </c>
       <c r="H75" s="17">
-        <v>0.0030120073675</v>
+        <v>0.0030443027599</v>
       </c>
       <c r="I75" s="16">
-        <v>9.18</v>
+        <v>8.63</v>
       </c>
       <c r="J75" s="11" t="s">
         <v>13</v>
@@ -3424,28 +3477,28 @@
     </row>
     <row r="76" spans="2:10" ht="15" customHeight="1">
       <c r="B76" s="12" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C76" s="13" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="D76" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F76" s="15">
         <v>165</v>
       </c>
       <c r="G76" s="16">
-        <v>1707.02</v>
+        <v>1744.48</v>
       </c>
       <c r="H76" s="17">
-        <v>0.0029973456552</v>
+        <v>0.0030430991127</v>
       </c>
       <c r="I76" s="16">
-        <v>9.12</v>
+        <v>8.83</v>
       </c>
       <c r="J76" s="11" t="s">
         <v>13</v>
@@ -3453,28 +3506,28 @@
     </row>
     <row r="77" spans="2:10" ht="15" customHeight="1">
       <c r="B77" s="12" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C77" s="13" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D77" s="14">
-        <v>9.54</v>
+        <v>9.58</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F77" s="15">
         <v>165</v>
       </c>
       <c r="G77" s="16">
-        <v>1697.94</v>
+        <v>1742.71</v>
       </c>
       <c r="H77" s="17">
-        <v>0.0029814021404</v>
+        <v>0.0030400114961</v>
       </c>
       <c r="I77" s="16">
-        <v>9.04</v>
+        <v>8.81</v>
       </c>
       <c r="J77" s="11" t="s">
         <v>13</v>
@@ -3482,28 +3535,28 @@
     </row>
     <row r="78" spans="2:10" ht="15" customHeight="1">
       <c r="B78" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="D78" s="14">
-        <v>8.45</v>
+        <v>9.58</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F78" s="15">
-        <v>1500</v>
+        <v>165</v>
       </c>
       <c r="G78" s="16">
-        <v>1502.85</v>
+        <v>1736.23</v>
       </c>
       <c r="H78" s="17">
-        <v>0.0026388448395</v>
+        <v>0.0030287076794</v>
       </c>
       <c r="I78" s="16">
-        <v>8.28</v>
+        <v>8.25</v>
       </c>
       <c r="J78" s="11" t="s">
         <v>13</v>
@@ -3511,28 +3564,28 @@
     </row>
     <row r="79" spans="2:10" ht="15" customHeight="1">
       <c r="B79" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D79" s="14">
-        <v>8.45</v>
+        <v>9.58</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F79" s="15">
-        <v>1500</v>
+        <v>165</v>
       </c>
       <c r="G79" s="16">
-        <v>1502.15</v>
+        <v>1735.83</v>
       </c>
       <c r="H79" s="17">
-        <v>0.0026376157139</v>
+        <v>0.0030280099129</v>
       </c>
       <c r="I79" s="16">
-        <v>8.32</v>
+        <v>7.06</v>
       </c>
       <c r="J79" s="11" t="s">
         <v>13</v>
@@ -3540,28 +3593,28 @@
     </row>
     <row r="80" spans="2:10" ht="15" customHeight="1">
       <c r="B80" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D80" s="14">
-        <v>8.45</v>
+        <v>9.58</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F80" s="15">
-        <v>1500</v>
+        <v>165</v>
       </c>
       <c r="G80" s="16">
-        <v>1499.60</v>
+        <v>1735.69</v>
       </c>
       <c r="H80" s="17">
-        <v>0.002633138185</v>
+        <v>0.0030277656946</v>
       </c>
       <c r="I80" s="16">
-        <v>8.38</v>
+        <v>7.64</v>
       </c>
       <c r="J80" s="11" t="s">
         <v>13</v>
@@ -3569,28 +3622,28 @@
     </row>
     <row r="81" spans="2:10" ht="15" customHeight="1">
       <c r="B81" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D81" s="14">
-        <v>8.45</v>
+        <v>9.58</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F81" s="15">
-        <v>1500</v>
+        <v>165</v>
       </c>
       <c r="G81" s="16">
-        <v>1498.02</v>
+        <v>1735.51</v>
       </c>
       <c r="H81" s="17">
-        <v>0.0026303638729</v>
+        <v>0.0030274516997</v>
       </c>
       <c r="I81" s="16">
-        <v>8.43</v>
+        <v>8.47</v>
       </c>
       <c r="J81" s="11" t="s">
         <v>13</v>
@@ -3598,28 +3651,28 @@
     </row>
     <row r="82" spans="2:10" ht="15" customHeight="1">
       <c r="B82" s="12" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D82" s="14">
-        <v>10.10</v>
+        <v>9.58</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="F82" s="15">
-        <v>1500</v>
+        <v>165</v>
       </c>
       <c r="G82" s="16">
-        <v>1491.15</v>
+        <v>1733.65</v>
       </c>
       <c r="H82" s="17">
-        <v>0.0026183008832</v>
+        <v>0.0030242070856</v>
       </c>
       <c r="I82" s="16">
-        <v>10.44</v>
+        <v>8.01</v>
       </c>
       <c r="J82" s="11" t="s">
         <v>13</v>
@@ -3627,28 +3680,28 @@
     </row>
     <row r="83" spans="2:10" ht="15" customHeight="1">
       <c r="B83" s="12" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C83" s="13" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D83" s="14">
-        <v>7.55</v>
+        <v>8.45</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F83" s="15">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G83" s="16">
-        <v>998.47</v>
+        <v>1519.63</v>
       </c>
       <c r="H83" s="17">
-        <v>0.0017532071776</v>
+        <v>0.0026508671379</v>
       </c>
       <c r="I83" s="16">
-        <v>7.61</v>
+        <v>7.34</v>
       </c>
       <c r="J83" s="11" t="s">
         <v>13</v>
@@ -3656,25 +3709,25 @@
     </row>
     <row r="84" spans="2:10" ht="15" customHeight="1">
       <c r="B84" s="12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C84" s="13" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D84" s="14">
-        <v>8.8</v>
+        <v>8.45</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F84" s="15">
-        <v>20</v>
+        <v>1500</v>
       </c>
       <c r="G84" s="16">
-        <v>209.94</v>
+        <v>1512.69</v>
       </c>
       <c r="H84" s="17">
-        <v>0.0003686323223</v>
+        <v>0.0026387608897</v>
       </c>
       <c r="I84" s="16">
         <v>7.39</v>
@@ -3685,28 +3738,28 @@
     </row>
     <row r="85" spans="2:10" ht="15" customHeight="1">
       <c r="B85" s="12" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="C85" s="13" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="D85" s="14">
-        <v>8.85</v>
+        <v>10.10</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="F85" s="15">
-        <v>5</v>
+        <v>1500</v>
       </c>
       <c r="G85" s="16">
-        <v>52.54</v>
+        <v>1507.82</v>
       </c>
       <c r="H85" s="17">
-        <v>0.0000922546547</v>
+        <v>0.0026302655829</v>
       </c>
       <c r="I85" s="16">
-        <v>7.39</v>
+        <v>9.76</v>
       </c>
       <c r="J85" s="11" t="s">
         <v>13</v>
@@ -3714,36 +3767,57 @@
     </row>
     <row r="86" spans="2:10" ht="15" customHeight="1">
       <c r="B86" s="12" t="s">
-        <v>13</v>
+        <v>144</v>
+      </c>
+      <c r="C86" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="D86" s="14">
+        <v>8.45</v>
+      </c>
+      <c r="E86" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" s="15">
+        <v>1500</v>
+      </c>
+      <c r="G86" s="16">
+        <v>1503.80</v>
+      </c>
+      <c r="H86" s="17">
+        <v>0.00262325303</v>
+      </c>
+      <c r="I86" s="16">
+        <v>7.30</v>
       </c>
       <c r="J86" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I87" s="9" t="s">
-        <v>13</v>
+      <c r="B87" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D87" s="14">
+        <v>8.8</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F87" s="15">
+        <v>20</v>
+      </c>
+      <c r="G87" s="16">
+        <v>214.74</v>
+      </c>
+      <c r="H87" s="17">
+        <v>0.0003745959274</v>
+      </c>
+      <c r="I87" s="16">
+        <v>6.62</v>
       </c>
       <c r="J87" s="11" t="s">
         <v>13</v>
@@ -3751,35 +3825,35 @@
     </row>
     <row r="88" spans="2:10" ht="15" customHeight="1">
       <c r="B88" s="12" t="s">
-        <v>13</v>
+        <v>149</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D88" s="14">
+        <v>8.85</v>
+      </c>
+      <c r="E88" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F88" s="15">
+        <v>5</v>
+      </c>
+      <c r="G88" s="16">
+        <v>53.70</v>
+      </c>
+      <c r="H88" s="17">
+        <v>0.000093675148</v>
+      </c>
+      <c r="I88" s="16">
+        <v>6.62</v>
       </c>
       <c r="J88" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I89" s="9" t="s">
+      <c r="B89" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J89" s="11" t="s">
@@ -3787,7 +3861,28 @@
       </c>
     </row>
     <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I90" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J90" s="11" t="s">
@@ -3795,28 +3890,7 @@
       </c>
     </row>
     <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I91" s="9" t="s">
+      <c r="B91" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J91" s="11" t="s">
@@ -3824,7 +3898,28 @@
       </c>
     </row>
     <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I92" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J92" s="11" t="s">
@@ -3832,28 +3927,7 @@
       </c>
     </row>
     <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I93" s="9" t="s">
+      <c r="B93" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J93" s="11" t="s">
@@ -3861,7 +3935,28 @@
       </c>
     </row>
     <row r="94" spans="2:10" ht="15" customHeight="1">
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I94" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J94" s="11" t="s">
@@ -3869,28 +3964,7 @@
       </c>
     </row>
     <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I95" s="9" t="s">
+      <c r="B95" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J95" s="11" t="s">
@@ -3898,7 +3972,28 @@
       </c>
     </row>
     <row r="96" spans="2:10" ht="15" customHeight="1">
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I96" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J96" s="11" t="s">
@@ -3906,28 +4001,7 @@
       </c>
     </row>
     <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I97" s="9" t="s">
+      <c r="B97" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J97" s="11" t="s">
@@ -3935,7 +4009,28 @@
       </c>
     </row>
     <row r="98" spans="2:10" ht="15" customHeight="1">
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H98" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I98" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J98" s="11" t="s">
@@ -3943,28 +4038,7 @@
       </c>
     </row>
     <row r="99" spans="2:10" ht="15" customHeight="1">
-      <c r="B99" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I99" s="9" t="s">
+      <c r="B99" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J99" s="11" t="s">
@@ -3972,7 +4046,28 @@
       </c>
     </row>
     <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I100" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J100" s="11" t="s">
@@ -3980,28 +4075,7 @@
       </c>
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
-      <c r="B101" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F101" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H101" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I101" s="9" t="s">
+      <c r="B101" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J101" s="11" t="s">
@@ -4009,7 +4083,28 @@
       </c>
     </row>
     <row r="102" spans="2:10" ht="15" customHeight="1">
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E102" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G102" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I102" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J102" s="11" t="s">
@@ -4017,28 +4112,7 @@
       </c>
     </row>
     <row r="103" spans="2:10" ht="15" customHeight="1">
-      <c r="B103" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D103" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F103" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G103" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H103" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I103" s="9" t="s">
+      <c r="B103" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J103" s="11" t="s">
@@ -4046,7 +4120,28 @@
       </c>
     </row>
     <row r="104" spans="2:10" ht="15" customHeight="1">
-      <c r="B104" s="12" t="s">
+      <c r="B104" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G104" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I104" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J104" s="11" t="s">
@@ -4054,28 +4149,7 @@
       </c>
     </row>
     <row r="105" spans="2:10" ht="15" customHeight="1">
-      <c r="B105" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D105" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F105" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G105" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H105" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I105" s="9" t="s">
+      <c r="B105" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J105" s="11" t="s">
@@ -4083,7 +4157,28 @@
       </c>
     </row>
     <row r="106" spans="2:10" ht="15" customHeight="1">
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I106" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J106" s="11" t="s">
@@ -4091,36 +4186,36 @@
       </c>
     </row>
     <row r="107" spans="2:10" ht="15" customHeight="1">
-      <c r="B107" s="7" t="s">
+      <c r="B107" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J107" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="2:10" ht="15" customHeight="1">
+      <c r="B108" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E108" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G108" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C107" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D107" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F107" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G107" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="H107" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="I107" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J107" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="2:10" ht="15" customHeight="1">
-      <c r="B108" s="12" t="s">
+      <c r="H108" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I108" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J108" s="11" t="s">
@@ -4128,28 +4223,7 @@
       </c>
     </row>
     <row r="109" spans="2:10" ht="15" customHeight="1">
-      <c r="B109" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F109" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" s="9">
-        <v>6411.320000000001</v>
-      </c>
-      <c r="H109" s="10">
-        <v>0.011257596364500001</v>
-      </c>
-      <c r="I109" s="9" t="s">
+      <c r="B109" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J109" s="11" t="s">
@@ -4157,28 +4231,28 @@
       </c>
     </row>
     <row r="110" spans="2:10" ht="15" customHeight="1">
-      <c r="B110" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="C110" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="F110" s="15">
-        <v>4200000</v>
-      </c>
-      <c r="G110" s="16">
-        <v>5409.60</v>
-      </c>
-      <c r="H110" s="17">
-        <v>0.0094986825324</v>
-      </c>
-      <c r="I110" s="16" t="s">
+      <c r="B110" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E110" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G110" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="I110" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J110" s="11" t="s">
@@ -4187,27 +4261,6 @@
     </row>
     <row r="111" spans="2:10" ht="15" customHeight="1">
       <c r="B111" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C111" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="F111" s="15">
-        <v>1010100</v>
-      </c>
-      <c r="G111" s="16">
-        <v>1001.72</v>
-      </c>
-      <c r="H111" s="17">
-        <v>0.0017589138321</v>
-      </c>
-      <c r="I111" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J111" s="11" t="s">
@@ -4215,7 +4268,28 @@
       </c>
     </row>
     <row r="112" spans="2:10" ht="15" customHeight="1">
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G112" s="9">
+        <v>6508.60</v>
+      </c>
+      <c r="H112" s="10">
+        <v>0.0113537070561</v>
+      </c>
+      <c r="I112" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J112" s="11" t="s">
@@ -4223,28 +4297,28 @@
       </c>
     </row>
     <row r="113" spans="2:10" ht="15" customHeight="1">
-      <c r="B113" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D113" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E113" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F113" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G113" s="9">
-        <v>10990.44</v>
-      </c>
-      <c r="H113" s="10">
-        <v>0.0192980443011</v>
-      </c>
-      <c r="I113" s="9" t="s">
+      <c r="B113" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C113" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="D113" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="F113" s="15">
+        <v>4200000</v>
+      </c>
+      <c r="G113" s="16">
+        <v>5580.12</v>
+      </c>
+      <c r="H113" s="17">
+        <v>0.0097340515346</v>
+      </c>
+      <c r="I113" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J113" s="11" t="s">
@@ -4253,25 +4327,25 @@
     </row>
     <row r="114" spans="2:10" ht="15" customHeight="1">
       <c r="B114" s="12" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C114" s="13" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D114" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F114" s="15">
-        <v>2592814</v>
+        <v>1010100</v>
       </c>
       <c r="G114" s="16">
-        <v>7729.96</v>
+        <v>928.48</v>
       </c>
       <c r="H114" s="17">
-        <v>0.0135729880265</v>
+        <v>0.0016196555215</v>
       </c>
       <c r="I114" s="16" t="s">
         <v>13</v>
@@ -4282,27 +4356,6 @@
     </row>
     <row r="115" spans="2:10" ht="15" customHeight="1">
       <c r="B115" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="C115" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E115" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="F115" s="15">
-        <v>533446</v>
-      </c>
-      <c r="G115" s="16">
-        <v>1995.09</v>
-      </c>
-      <c r="H115" s="17">
-        <v>0.0035031659519</v>
-      </c>
-      <c r="I115" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J115" s="11" t="s">
@@ -4310,28 +4363,28 @@
       </c>
     </row>
     <row r="116" spans="2:10" ht="15" customHeight="1">
-      <c r="B116" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="C116" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="D116" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="F116" s="15">
-        <v>341867</v>
-      </c>
-      <c r="G116" s="16">
-        <v>1265.39</v>
-      </c>
-      <c r="H116" s="17">
-        <v>0.0022218903227</v>
-      </c>
-      <c r="I116" s="16" t="s">
+      <c r="B116" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G116" s="9">
+        <v>29898.440000000002</v>
+      </c>
+      <c r="H116" s="10">
+        <v>0.052155322065599995</v>
+      </c>
+      <c r="I116" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J116" s="11" t="s">
@@ -4340,6 +4393,27 @@
     </row>
     <row r="117" spans="2:10" ht="15" customHeight="1">
       <c r="B117" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="C117" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="D117" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F117" s="15">
+        <v>5110812</v>
+      </c>
+      <c r="G117" s="16">
+        <v>19492.64</v>
+      </c>
+      <c r="H117" s="17">
+        <v>0.0340032763285</v>
+      </c>
+      <c r="I117" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J117" s="11" t="s">
@@ -4347,28 +4421,28 @@
       </c>
     </row>
     <row r="118" spans="2:10" ht="15" customHeight="1">
-      <c r="B118" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C118" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D118" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="9">
-        <v>1757.58</v>
-      </c>
-      <c r="H118" s="10">
-        <v>0.0030861236404</v>
-      </c>
-      <c r="I118" s="9" t="s">
+      <c r="B118" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C118" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D118" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F118" s="15">
+        <v>2592814</v>
+      </c>
+      <c r="G118" s="16">
+        <v>7932.46</v>
+      </c>
+      <c r="H118" s="17">
+        <v>0.0138375114579</v>
+      </c>
+      <c r="I118" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J118" s="11" t="s">
@@ -4377,10 +4451,10 @@
     </row>
     <row r="119" spans="2:10" ht="15" customHeight="1">
       <c r="B119" s="12" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C119" s="13" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D119" s="13" t="s">
         <v>13</v>
@@ -4389,13 +4463,13 @@
         <v>170</v>
       </c>
       <c r="F119" s="15">
-        <v>16108.90</v>
+        <v>533446</v>
       </c>
       <c r="G119" s="16">
-        <v>1757.58</v>
+        <v>2107.01</v>
       </c>
       <c r="H119" s="17">
-        <v>0.0030861236404</v>
+        <v>0.0036755023053</v>
       </c>
       <c r="I119" s="16" t="s">
         <v>13</v>
@@ -4406,6 +4480,27 @@
     </row>
     <row r="120" spans="2:10" ht="15" customHeight="1">
       <c r="B120" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="C120" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F120" s="15">
+        <v>271555</v>
+      </c>
+      <c r="G120" s="16">
+        <v>366.33</v>
+      </c>
+      <c r="H120" s="17">
+        <v>0.0006390319739</v>
+      </c>
+      <c r="I120" s="16" t="s">
         <v>13</v>
       </c>
       <c r="J120" s="11" t="s">
@@ -4413,28 +4508,7 @@
       </c>
     </row>
     <row r="121" spans="2:10" ht="15" customHeight="1">
-      <c r="B121" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D121" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F121" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G121" s="9">
-        <v>18358.99</v>
-      </c>
-      <c r="H121" s="10">
-        <v>0.0322364347874</v>
-      </c>
-      <c r="I121" s="9" t="s">
+      <c r="B121" s="12" t="s">
         <v>13</v>
       </c>
       <c r="J121" s="11" t="s">
@@ -4442,7 +4516,28 @@
       </c>
     </row>
     <row r="122" spans="2:10" ht="15" customHeight="1">
-      <c r="B122" s="12" t="s">
+      <c r="B122" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E122" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G122" s="9">
+        <v>1802.74</v>
+      </c>
+      <c r="H122" s="10">
+        <v>0.0031447287985</v>
+      </c>
+      <c r="I122" s="9" t="s">
         <v>13</v>
       </c>
       <c r="J122" s="11" t="s">
@@ -4450,179 +4545,393 @@
       </c>
     </row>
     <row r="123" spans="2:10" ht="15" customHeight="1">
-      <c r="B123" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="C123" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D123" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E123" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F123" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="19">
-        <v>17216.589125419967</v>
-      </c>
-      <c r="H123" s="20">
-        <v>0.03023050029460201</v>
-      </c>
-      <c r="I123" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J123" s="21" t="s">
+      <c r="B123" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="C123" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F123" s="15">
+        <v>16108.90</v>
+      </c>
+      <c r="G123" s="16">
+        <v>1802.74</v>
+      </c>
+      <c r="H123" s="17">
+        <v>0.0031447287985</v>
+      </c>
+      <c r="I123" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J123" s="11" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="124" spans="2:10" ht="15" customHeight="1">
-      <c r="B124" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="C124" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D124" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E124" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G124" s="19">
-        <v>569510.55912542</v>
-      </c>
-      <c r="H124" s="20">
-        <v>0.999999999996602</v>
-      </c>
-      <c r="I124" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J124" s="21" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="2:9" ht="15" customHeight="1">
-      <c r="B127" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="C127" s="22"/>
-      <c r="D127" s="22"/>
-      <c r="E127" s="22"/>
-      <c r="F127" s="22"/>
-      <c r="G127" s="22"/>
-      <c r="H127" s="22"/>
-      <c r="I127" s="22"/>
-    </row>
-    <row r="128" spans="2:8" ht="15" customHeight="1">
-      <c r="B128" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="C128" s="22"/>
-      <c r="D128" s="22"/>
-      <c r="E128" s="22"/>
-      <c r="F128" s="22"/>
-      <c r="G128" s="22"/>
-      <c r="H128" s="22"/>
-    </row>
-    <row r="129" spans="2:8" ht="15" customHeight="1">
-      <c r="B129" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="C129" s="22"/>
-      <c r="D129" s="22"/>
-      <c r="E129" s="22"/>
-      <c r="F129" s="22"/>
-      <c r="G129" s="22"/>
-      <c r="H129" s="22"/>
-    </row>
-    <row r="130" spans="2:8" ht="15" customHeight="1">
-      <c r="B130" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="C130" s="22"/>
-      <c r="D130" s="22"/>
-      <c r="E130" s="22"/>
-      <c r="F130" s="22"/>
-      <c r="G130" s="22"/>
-      <c r="H130" s="22"/>
-    </row>
-    <row r="131" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B131" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="C131" s="22"/>
-      <c r="D131" s="22"/>
-      <c r="E131" s="22"/>
-      <c r="F131" s="22"/>
-      <c r="G131" s="22"/>
-      <c r="H131" s="22"/>
-    </row>
-    <row r="132" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B132" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="C132" s="22"/>
-      <c r="D132" s="22"/>
-      <c r="E132" s="22"/>
-      <c r="F132" s="22"/>
-      <c r="G132" s="22"/>
-      <c r="H132" s="22"/>
-    </row>
-    <row r="133" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B133" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="C133" s="22"/>
-      <c r="D133" s="22"/>
-      <c r="E133" s="22"/>
-      <c r="F133" s="22"/>
-      <c r="G133" s="22"/>
-      <c r="H133" s="22"/>
-    </row>
-    <row r="134" spans="2:7" ht="46.5" customHeight="1">
-      <c r="B134" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="C134" s="24"/>
-      <c r="D134" s="24"/>
-      <c r="E134" s="24"/>
-      <c r="F134" s="24"/>
-      <c r="G134" s="24"/>
-    </row>
-    <row r="137" ht="15">
-      <c r="B137" s="22" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="152" ht="15">
-      <c r="B152" s="22" t="s">
+      <c r="B124" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J124" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="2:10" ht="15" customHeight="1">
+      <c r="B125" s="7" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="153" ht="15">
-      <c r="B153" s="22" t="s">
+      <c r="C125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G125" s="9">
+        <v>4852.22</v>
+      </c>
+      <c r="H125" s="10">
+        <v>0.0084642910076</v>
+      </c>
+      <c r="I125" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J125" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="126" spans="2:10" ht="15" customHeight="1">
+      <c r="B126" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J126" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="2:10" ht="15" customHeight="1">
+      <c r="B127" s="18" t="s">
         <v>184</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E127" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G127" s="19">
+        <v>14681.090571799898</v>
+      </c>
+      <c r="H127" s="20">
+        <v>0.025609931723823576</v>
+      </c>
+      <c r="I127" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J127" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="2:10" ht="15" customHeight="1">
+      <c r="B128" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C128" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D128" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" s="19">
+        <v>573257.7005718</v>
+      </c>
+      <c r="H128" s="20">
+        <v>0.9999999999954235</v>
+      </c>
+      <c r="I128" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J128" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" ht="15" customHeight="1">
+      <c r="B129" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H129" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="I129" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J129" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" ht="15" customHeight="1">
+      <c r="B130" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="G130" s="19">
+        <v>-7500</v>
+      </c>
+      <c r="H130" s="20">
+        <v>-0.013083121242887921</v>
+      </c>
+      <c r="I130" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" s="21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" ht="15" customHeight="1">
+      <c r="B131" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" s="16">
+        <v>-5000</v>
+      </c>
+      <c r="H131" s="17">
+        <v>-0.008722080828591947</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J131" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10" ht="15" customHeight="1">
+      <c r="B132" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G132" s="16">
+        <v>-2500</v>
+      </c>
+      <c r="H132" s="17">
+        <v>-0.0043610404142959735</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J132" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="2:10" ht="15" customHeight="1">
+      <c r="B133" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C133" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D133" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E133" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="G133" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H133" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I133" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="J133" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="136" spans="2:9" ht="15" customHeight="1">
+      <c r="B136" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C136" s="23"/>
+      <c r="D136" s="23"/>
+      <c r="E136" s="23"/>
+      <c r="F136" s="23"/>
+      <c r="G136" s="23"/>
+      <c r="H136" s="23"/>
+      <c r="I136" s="23"/>
+    </row>
+    <row r="137" spans="2:8" ht="15" customHeight="1">
+      <c r="B137" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C137" s="23"/>
+      <c r="D137" s="23"/>
+      <c r="E137" s="23"/>
+      <c r="F137" s="23"/>
+      <c r="G137" s="23"/>
+      <c r="H137" s="23"/>
+    </row>
+    <row r="138" spans="2:8" ht="15" customHeight="1">
+      <c r="B138" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C138" s="23"/>
+      <c r="D138" s="23"/>
+      <c r="E138" s="23"/>
+      <c r="F138" s="23"/>
+      <c r="G138" s="23"/>
+      <c r="H138" s="23"/>
+    </row>
+    <row r="139" spans="2:8" ht="15" customHeight="1">
+      <c r="B139" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C139" s="23"/>
+      <c r="D139" s="23"/>
+      <c r="E139" s="23"/>
+      <c r="F139" s="23"/>
+      <c r="G139" s="23"/>
+      <c r="H139" s="23"/>
+    </row>
+    <row r="140" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B140" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="C140" s="23"/>
+      <c r="D140" s="23"/>
+      <c r="E140" s="23"/>
+      <c r="F140" s="23"/>
+      <c r="G140" s="23"/>
+      <c r="H140" s="23"/>
+    </row>
+    <row r="141" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B141" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="C141" s="23"/>
+      <c r="D141" s="23"/>
+      <c r="E141" s="23"/>
+      <c r="F141" s="23"/>
+      <c r="G141" s="23"/>
+      <c r="H141" s="23"/>
+    </row>
+    <row r="142" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B142" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="C142" s="23"/>
+      <c r="D142" s="23"/>
+      <c r="E142" s="23"/>
+      <c r="F142" s="23"/>
+      <c r="G142" s="23"/>
+      <c r="H142" s="23"/>
+    </row>
+    <row r="143" spans="2:7" ht="45.75" customHeight="1">
+      <c r="B143" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="C143" s="25"/>
+      <c r="D143" s="25"/>
+      <c r="E143" s="25"/>
+      <c r="F143" s="25"/>
+      <c r="G143" s="25"/>
+    </row>
+    <row r="146" ht="15">
+      <c r="B146" s="23" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="161" ht="15">
+      <c r="B161" s="23" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B134:G134"/>
-    <mergeCell ref="B129:H129"/>
-    <mergeCell ref="B130:H130"/>
-    <mergeCell ref="B131:H131"/>
-    <mergeCell ref="B132:H132"/>
-    <mergeCell ref="B133:H133"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B127:I127"/>
-    <mergeCell ref="B128:H128"/>
+    <mergeCell ref="B136:I136"/>
+    <mergeCell ref="B137:H137"/>
+    <mergeCell ref="B143:G143"/>
+    <mergeCell ref="B138:H138"/>
+    <mergeCell ref="B139:H139"/>
+    <mergeCell ref="B140:H140"/>
+    <mergeCell ref="B141:H141"/>
+    <mergeCell ref="B142:H142"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
